--- a/artfynd/A 6245-2024 artfynd.xlsx
+++ b/artfynd/A 6245-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Brorsson, Amanda Fränkel</t>
+          <t>Amanda Fränkel, Christina Brorsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
